--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 2482-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 15565-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,39 +2853,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -2909,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2993,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3007,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>46174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,16 +3023,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3051,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3067,42 +3063,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3112,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46174</v>
+        <v>45401</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,13 +3128,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3172,35 +3168,39 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46213</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44704</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45463</v>
+        <v>45104</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45117</v>
+        <v>46021</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3545,14 +3545,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45005</v>
+        <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45117</v>
+        <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44524</v>
+        <v>46021</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45030</v>
+        <v>46021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44907</v>
+        <v>46021</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.9</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44897</v>
+        <v>44907</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45401</v>
+        <v>45463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4129,14 +4129,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45048</v>
+        <v>44897</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>8.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45406</v>
+        <v>44897</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45233</v>
+        <v>45232</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46021</v>
+        <v>45950</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46021</v>
+        <v>46191</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46021</v>
+        <v>45233</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46021</v>
+        <v>45232</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4640,14 +4640,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46021</v>
+        <v>45400</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45428</v>
+        <v>46181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45232</v>
+        <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45240</v>
+        <v>46176</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45950</v>
+        <v>45117</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45232</v>
+        <v>45401</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46191</v>
+        <v>45428</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45400</v>
+        <v>44741</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>8.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44741</v>
+        <v>45406</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.9</v>
+        <v>13.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5297,14 +5297,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45104</v>
+        <v>45005</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.1</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5370,14 +5370,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45232</v>
+        <v>45048</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46181</v>
+        <v>45232</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46176</v>
+        <v>44524</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46181</v>
+        <v>45030</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>45427</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>46213</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>46213</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14150-2023</t>
+          <t>A 31700-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45009</v>
+        <v>45117</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1318,22 +1318,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1342,10 +1342,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1354,9 +1354,121 @@
         <v>7</v>
       </c>
       <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Brun glada
+Revig blodrot
+Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31700-2023 artfynd.xlsx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31700-2023 karta.png", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31700-2023 georefererad karta.tif", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31700-2023 FSC-klagomål.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31700-2023 FSC-klagomål mail.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31700-2023 tillsynsbegäran.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31700-2023 tillsynsbegäran mail.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 31700-2023 prioriterade fågelarter.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 14150-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45009</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Guldlockmossa
 Lönnlav
@@ -1364,144 +1476,32 @@
 Tibast</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 14150-2023 artfynd.xlsx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 14150-2023 karta.png", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 14150-2023 georefererad karta.tif", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 14150-2023 FSC-klagomål.docx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 14150-2023 FSC-klagomål mail.docx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 14150-2023 tillsynsbegäran.docx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 14150-2023 tillsynsbegäran mail.docx", "A 14150-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 31700-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Brun glada
-Revig blodrot
-Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31700-2023 artfynd.xlsx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31700-2023 karta.png", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31700-2023 georefererad karta.tif", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31700-2023 FSC-klagomål.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31700-2023 FSC-klagomål mail.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31700-2023 tillsynsbegäran.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31700-2023 tillsynsbegäran mail.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 31700-2023 prioriterade fågelarter.docx", "A 31700-2023")</f>
         <v/>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2482-2025</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45674</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,35 +2853,39 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -2905,7 +2909,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2997,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3007,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46174</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3023,16 +3027,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>11.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3047,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3063,42 +3067,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3112,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45401</v>
+        <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3128,13 +3132,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3168,39 +3172,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46213</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44704</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45104</v>
+        <v>45232</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46021</v>
+        <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45240</v>
+        <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3691,14 +3691,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46021</v>
+        <v>45005</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46021</v>
+        <v>44524</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46021</v>
+        <v>45030</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46021</v>
+        <v>44907</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44907</v>
+        <v>44897</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>8.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4129,14 +4129,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44897</v>
+        <v>45400</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.9</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44897</v>
+        <v>45401</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45232</v>
+        <v>44741</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45950</v>
+        <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46191</v>
+        <v>45048</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45233</v>
+        <v>45950</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45232</v>
+        <v>45406</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>13.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4640,14 +4640,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45400</v>
+        <v>45233</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46181</v>
+        <v>46021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.3</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46181</v>
+        <v>46021</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46176</v>
+        <v>46021</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45117</v>
+        <v>46021</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45401</v>
+        <v>45104</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45428</v>
+        <v>46191</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44741</v>
+        <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45406</v>
+        <v>45428</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>13.5</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5297,14 +5297,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45005</v>
+        <v>45232</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5370,14 +5370,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45048</v>
+        <v>45240</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45232</v>
+        <v>46181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44524</v>
+        <v>46176</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.1</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45030</v>
+        <v>46181</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>45427</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>46213</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>46213</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31700-2023</t>
+          <t>A 14150-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45117</v>
+        <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1318,22 +1318,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1342,10 +1342,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1354,9 +1354,117 @@
         <v>7</v>
       </c>
       <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Guldlockmossa
+Lönnlav
+Platt fjädermossa
+Tibast</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 14150-2023 artfynd.xlsx", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 14150-2023 karta.png", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 14150-2023 georefererad karta.tif", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 14150-2023 FSC-klagomål.docx", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 14150-2023 FSC-klagomål mail.docx", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 14150-2023 tillsynsbegäran.docx", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 14150-2023 tillsynsbegäran mail.docx", "A 14150-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 31700-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Brun glada
 Revig blodrot
@@ -1364,144 +1472,36 @@
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31700-2023 artfynd.xlsx", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31700-2023 karta.png", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31700-2023 georefererad karta.tif", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31700-2023 FSC-klagomål.docx", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31700-2023 FSC-klagomål mail.docx", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31700-2023 tillsynsbegäran.docx", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31700-2023 tillsynsbegäran mail.docx", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 31700-2023 prioriterade fågelarter.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 14150-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45009</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Guldlockmossa
-Lönnlav
-Platt fjädermossa
-Tibast</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 14150-2023 artfynd.xlsx", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 14150-2023 karta.png", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 14150-2023 georefererad karta.tif", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 14150-2023 FSC-klagomål.docx", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 14150-2023 FSC-klagomål mail.docx", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 14150-2023 tillsynsbegäran.docx", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 14150-2023 tillsynsbegäran mail.docx", "A 14150-2023")</f>
         <v/>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 2482-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 15565-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U15" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D16" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="D17" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Mindre tåtelsmygare
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,39 +2853,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -2909,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2993,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3014,7 +3010,7 @@
         <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,16 +3023,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3051,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3067,35 +3063,39 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
         <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46213</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44704</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45232</v>
+        <v>45104</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45463</v>
+        <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45117</v>
+        <v>45240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45117</v>
+        <v>44907</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3691,14 +3691,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45005</v>
+        <v>45463</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44524</v>
+        <v>46021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45030</v>
+        <v>46021</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44907</v>
+        <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.9</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4129,14 +4129,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45400</v>
+        <v>44897</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>8.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45401</v>
+        <v>44897</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44741</v>
+        <v>45232</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46021</v>
+        <v>45233</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45048</v>
+        <v>45232</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45950</v>
+        <v>45400</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45406</v>
+        <v>45950</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>13.5</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45233</v>
+        <v>46191</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46021</v>
+        <v>45401</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46021</v>
+        <v>45428</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46021</v>
+        <v>44741</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>8.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45104</v>
+        <v>45406</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.1</v>
+        <v>13.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46191</v>
+        <v>45005</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45232</v>
+        <v>45048</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45428</v>
+        <v>45232</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45232</v>
+        <v>44524</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>8.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45240</v>
+        <v>46181</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>7.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
         <v>46181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46176</v>
+        <v>45030</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46181</v>
+        <v>46176</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>45427</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>46213</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>46213</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2482-2025</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45674</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,556 +1669,556 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 58350-2025</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>6.9</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="D16" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
       <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
         <v/>
@@ -2268,7 +2268,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,42 +2853,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2902,10 +2906,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45030</v>
+        <v>46174</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2918,19 +2922,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.1</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2942,58 +2946,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3007,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>45030</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3023,10 +3027,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3035,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3047,62 +3051,58 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46174</v>
+        <v>45401</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,16 +3132,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>11.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3172,35 +3172,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46213</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44704</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45104</v>
+        <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45240</v>
+        <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44907</v>
+        <v>45005</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45463</v>
+        <v>44524</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46021</v>
+        <v>45030</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46021</v>
+        <v>44907</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>8.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46021</v>
+        <v>45401</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4129,14 +4129,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44897</v>
+        <v>45048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.9</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44897</v>
+        <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>13.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45233</v>
+        <v>45950</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45232</v>
+        <v>46191</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45400</v>
+        <v>45428</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45950</v>
+        <v>45232</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46191</v>
+        <v>45240</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45117</v>
+        <v>45232</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45401</v>
+        <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45428</v>
+        <v>45400</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44741</v>
+        <v>46021</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.9</v>
+        <v>6.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45406</v>
+        <v>44741</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>13.5</v>
+        <v>8.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45005</v>
+        <v>46181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45048</v>
+        <v>46176</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45232</v>
+        <v>45104</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>8.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44524</v>
+        <v>45232</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46181</v>
+        <v>46021</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.3</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46181</v>
+        <v>46021</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45030</v>
+        <v>46021</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46176</v>
+        <v>46021</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>45427</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>46213</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>46213</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 58350-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 15565-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U14" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D15" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 2482-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45674</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>0.5</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,46 +2853,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2906,10 +2902,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46174</v>
+        <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,19 +2918,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>6.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2946,58 +2942,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3007,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45030</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,10 +3023,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3039,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3051,58 +3047,62 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45401</v>
+        <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,16 +3132,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3172,35 +3172,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46213</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44704</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45463</v>
+        <v>45104</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45117</v>
+        <v>45240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45005</v>
+        <v>44907</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44524</v>
+        <v>45463</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45030</v>
+        <v>44897</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44907</v>
+        <v>44897</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44897</v>
+        <v>45232</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44897</v>
+        <v>45233</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45401</v>
+        <v>45232</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45048</v>
+        <v>45400</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45406</v>
+        <v>46021</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45233</v>
+        <v>45950</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45950</v>
+        <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46191</v>
+        <v>46021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45428</v>
+        <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45240</v>
+        <v>46191</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45232</v>
+        <v>45117</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46181</v>
+        <v>45401</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45400</v>
+        <v>45428</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46021</v>
+        <v>44741</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.4</v>
+        <v>8.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44741</v>
+        <v>45406</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.9</v>
+        <v>13.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46181</v>
+        <v>45005</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46176</v>
+        <v>45048</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45104</v>
+        <v>45232</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.1</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45232</v>
+        <v>44524</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46021</v>
+        <v>45030</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46021</v>
+        <v>45427</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46021</v>
+        <v>46181</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46021</v>
+        <v>46176</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45427</v>
+        <v>46181</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>7.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5742,7 +5742,7 @@
         <v>46213</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>46213</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45160</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45401</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>46070</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45674</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46213</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44704</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45104</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44907</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45463</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>44897</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>44897</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45232</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45233</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45232</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45400</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>46021</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45950</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>46021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>46191</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45117</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45401</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45428</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44741</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45406</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45005</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45048</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45232</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44524</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45030</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>45427</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>46181</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>46176</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>46181</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>46213</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>46213</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE61"/>
+  <dimension ref="A1:AE67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45160</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45401</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 9570-2026</t>
+          <t>A 25022-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46070</v>
+        <v>46174</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2102,149 +2102,149 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
         <v>45674</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>46174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3023,13 +3023,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3063,46 +3063,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3112,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46174</v>
+        <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,19 +3128,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3156,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3172,59 +3168,59 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S 1996-2026</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46213</v>
+        <v>45401</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,7 +3233,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3249,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3261,10 +3257,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3277,63 +3273,63 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/S 1996-2026 artfynd.xlsx", "S 1996-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/S 1996-2026 karta.png", "S 1996-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/S 1996-2026 georefererad karta.tif", "S 1996-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/S 1996-2026 FSC-klagomål.docx", "S 1996-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/S 1996-2026 FSC-klagomål mail.docx", "S 1996-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/S 1996-2026 tillsynsbegäran.docx", "S 1996-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/S 1996-2026 tillsynsbegäran mail.docx", "S 1996-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/S 1996-2026 prioriterade fågelarter.docx", "S 1996-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21072-2022</t>
+          <t>S 1996-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44704</v>
+        <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3346,10 +3342,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3358,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3370,26 +3366,62 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/S 1996-2026 artfynd.xlsx", "S 1996-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/S 1996-2026 karta.png", "S 1996-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/S 1996-2026 georefererad karta.tif", "S 1996-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/S 1996-2026 FSC-klagomål.docx", "S 1996-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/S 1996-2026 FSC-klagomål mail.docx", "S 1996-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/S 1996-2026 tillsynsbegäran.docx", "S 1996-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/S 1996-2026 tillsynsbegäran mail.docx", "S 1996-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/S 1996-2026 prioriterade fågelarter.docx", "S 1996-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 21072-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3399,14 +3431,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45104</v>
+        <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3419,7 +3451,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.1</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3462,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3476,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45117</v>
+        <v>45104</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3492,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3535,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3549,10 +3581,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45240</v>
+        <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3565,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3608,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3622,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44907</v>
+        <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3638,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3681,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3695,10 +3727,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45463</v>
+        <v>44907</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3711,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3754,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3768,10 +3800,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3784,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3827,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3844,7 +3876,7 @@
         <v>44897</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3857,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3900,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3914,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45232</v>
+        <v>44897</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3973,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3987,10 +4019,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45233</v>
+        <v>45232</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4003,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4046,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4060,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45232</v>
+        <v>45950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4076,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4119,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4129,14 +4161,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45400</v>
+        <v>45233</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4149,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4209,7 +4241,7 @@
         <v>46021</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4265,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4279,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45950</v>
+        <v>45232</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4295,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4338,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4352,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46021</v>
+        <v>46191</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4368,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4411,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4428,7 +4460,7 @@
         <v>46021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4441,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4501,7 +4533,7 @@
         <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4514,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4574,7 +4606,7 @@
         <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4587,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4630,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4644,10 +4676,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46191</v>
+        <v>46021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4660,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4703,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4713,14 +4745,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45117</v>
+        <v>45400</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4733,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4776,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4790,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45401</v>
+        <v>45117</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4806,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4849,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4863,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45428</v>
+        <v>45401</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4879,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4922,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4936,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44741</v>
+        <v>45428</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4952,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.9</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4995,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5009,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45406</v>
+        <v>44741</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5025,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>13.5</v>
+        <v>8.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5068,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5078,14 +5110,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45005</v>
+        <v>45406</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5098,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>13.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5141,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5155,10 +5187,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45048</v>
+        <v>45005</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5171,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5214,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5228,10 +5260,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45232</v>
+        <v>46176</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5244,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5287,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5297,14 +5329,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44524</v>
+        <v>45048</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5317,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5360,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5374,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45030</v>
+        <v>46286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5390,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5433,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5447,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45427</v>
+        <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5463,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5523,7 +5555,7 @@
         <v>46181</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5579,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5593,10 +5625,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46176</v>
+        <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5609,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5652,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5666,10 +5698,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5682,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.3</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5725,148 +5757,586 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
+          <t>A 38847-2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>A 26073-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>A 54284-2023</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>45232</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>A 67456-2021</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>44524</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A 16690-2023</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>45030</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>A 18888-2024</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>45427</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>S 1997-2026</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D60" s="1" t="n">
+      <c r="D66" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="E60" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
+      <c r="E66" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
         <v>1.8</v>
       </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>S 1995-2026</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D61" s="1" t="n">
+      <c r="D67" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="E61" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
+      <c r="E67" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
         <v>1.8</v>
       </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 58350-2025</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45985</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,582 +1669,582 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D15" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="D16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Mindre tåtelsmygare
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
         <v/>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
         <v>45674</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,42 +2853,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2902,10 +2906,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45030</v>
+        <v>46286</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2918,10 +2922,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2951,42 +2955,42 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
@@ -3010,7 +3014,7 @@
         <v>46174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3102,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3112,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46286</v>
+        <v>45030</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3128,10 +3132,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3161,49 +3165,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3220,7 +3224,7 @@
         <v>45401</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3233,16 +3237,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3257,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3273,39 +3277,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45104</v>
+        <v>45427</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.1</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45117</v>
+        <v>45048</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45240</v>
+        <v>45463</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44907</v>
+        <v>45406</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45463</v>
+        <v>45233</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44897</v>
+        <v>45117</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.9</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44897</v>
+        <v>45117</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45232</v>
+        <v>45005</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45950</v>
+        <v>44524</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45233</v>
+        <v>45030</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46021</v>
+        <v>44907</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45232</v>
+        <v>44897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>8.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46191</v>
+        <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46021</v>
+        <v>45428</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46021</v>
+        <v>45232</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46021</v>
+        <v>45401</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46021</v>
+        <v>45240</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45400</v>
+        <v>45232</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45117</v>
+        <v>46021</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45401</v>
+        <v>46176</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45428</v>
+        <v>46286</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44741</v>
+        <v>46286</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45406</v>
+        <v>46021</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>13.5</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45005</v>
+        <v>46021</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46176</v>
+        <v>46021</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45048</v>
+        <v>46021</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5409,7 +5409,7 @@
         <v>46286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5482,7 +5482,7 @@
         <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5621,14 +5621,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46286</v>
+        <v>45400</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>7.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46181</v>
+        <v>44741</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45232</v>
+        <v>45104</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>8.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44524</v>
+        <v>45232</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45030</v>
+        <v>45950</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45427</v>
+        <v>46191</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 58350-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,450 +1669,450 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 15565-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U14" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D15" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
       <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
         <v/>
@@ -2162,7 +2162,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45674</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,46 +2853,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2906,10 +2902,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46286</v>
+        <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,10 +2918,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2955,49 +2951,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3007,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46174</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,13 +3023,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3067,42 +3063,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45030</v>
+        <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3165,49 +3165,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45401</v>
+        <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,16 +3237,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3277,35 +3277,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45427</v>
+        <v>45104</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.5</v>
+        <v>8.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45048</v>
+        <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45463</v>
+        <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45406</v>
+        <v>44907</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>13.5</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45233</v>
+        <v>45463</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45117</v>
+        <v>44897</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>8.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45117</v>
+        <v>44897</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45005</v>
+        <v>45232</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44524</v>
+        <v>45233</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45030</v>
+        <v>45232</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44907</v>
+        <v>46021</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4307,14 +4307,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44897</v>
+        <v>45400</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8.9</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45428</v>
+        <v>46021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45401</v>
+        <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45240</v>
+        <v>45950</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45232</v>
+        <v>46191</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46176</v>
+        <v>45401</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46286</v>
+        <v>45428</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46286</v>
+        <v>44741</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46021</v>
+        <v>45406</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>13.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46021</v>
+        <v>45005</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46021</v>
+        <v>45048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46021</v>
+        <v>45232</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46286</v>
+        <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>8.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46286</v>
+        <v>45030</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46286</v>
+        <v>46176</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5621,14 +5621,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45400</v>
+        <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44741</v>
+        <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.9</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45104</v>
+        <v>46286</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.1</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45232</v>
+        <v>45427</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45950</v>
+        <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46191</v>
+        <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 58350-2025</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45985</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D14" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="D17" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Mindre tåtelsmygare
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,42 +2853,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2902,10 +2906,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45030</v>
+        <v>46286</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2918,10 +2922,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2951,49 +2955,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3007,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>46174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3023,13 +3027,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3063,46 +3067,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46286</v>
+        <v>45030</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3165,49 +3165,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46174</v>
+        <v>45401</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,16 +3237,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>11.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3277,35 +3277,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45104</v>
+        <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45240</v>
+        <v>46021</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44907</v>
+        <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3796,14 +3796,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45463</v>
+        <v>45005</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44897</v>
+        <v>44524</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45233</v>
+        <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46021</v>
+        <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4307,14 +4307,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45400</v>
+        <v>44907</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46021</v>
+        <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4599,14 +4599,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46021</v>
+        <v>45048</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45950</v>
+        <v>45406</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>13.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46191</v>
+        <v>45233</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45117</v>
+        <v>45950</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45401</v>
+        <v>46191</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
         <v>45428</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44741</v>
+        <v>45232</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.9</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45406</v>
+        <v>45240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>13.5</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45005</v>
+        <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45048</v>
+        <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44524</v>
+        <v>46286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.1</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45030</v>
+        <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5548,14 +5548,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46176</v>
+        <v>45400</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5628,7 +5628,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46286</v>
+        <v>44741</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>8.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46286</v>
+        <v>46176</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45427</v>
+        <v>45104</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>8.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46181</v>
+        <v>45232</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46181</v>
+        <v>45427</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45674</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45160</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>46286</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>46174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45030</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45401</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>46021</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45005</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44524</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>46021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44907</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>44897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45048</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45406</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>45233</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45950</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>46191</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45428</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45232</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>45240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>46286</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>46286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45400</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>46181</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44741</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46181</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>46176</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45104</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45232</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>45427</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45674</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45160</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>46286</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>46174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45030</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45401</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>46021</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45005</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44524</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>46021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44907</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>44897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45048</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45406</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>45233</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45950</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>46191</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45428</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45232</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>45240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>46286</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>46286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45400</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>46181</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44741</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46181</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>46176</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45104</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45232</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>45427</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 2482-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,556 +1669,556 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 15565-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U15" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D16" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
       <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
         <v/>
@@ -2268,7 +2268,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,46 +2853,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2906,10 +2902,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46286</v>
+        <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,10 +2918,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2955,49 +2951,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3007,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46174</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,13 +3023,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3067,42 +3063,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45030</v>
+        <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3165,49 +3165,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45401</v>
+        <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,16 +3237,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3277,35 +3277,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45463</v>
+        <v>45427</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45117</v>
+        <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45117</v>
+        <v>45240</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3796,14 +3796,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45005</v>
+        <v>46021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44524</v>
+        <v>44907</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.1</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46021</v>
+        <v>45463</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4022,7 +4022,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4095,7 +4095,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4168,7 +4168,7 @@
         <v>46021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45030</v>
+        <v>46021</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44907</v>
+        <v>44897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>8.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4387,7 +4387,7 @@
         <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44897</v>
+        <v>45232</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45401</v>
+        <v>45233</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4599,14 +4599,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45048</v>
+        <v>45232</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45406</v>
+        <v>45400</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>13.5</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45233</v>
+        <v>45950</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45950</v>
+        <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46191</v>
+        <v>45117</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45428</v>
+        <v>45401</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45232</v>
+        <v>45428</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45240</v>
+        <v>44741</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45232</v>
+        <v>45406</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>13.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46286</v>
+        <v>45005</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46286</v>
+        <v>45048</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46286</v>
+        <v>45232</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46286</v>
+        <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>8.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5548,14 +5548,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45400</v>
+        <v>45030</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5628,7 +5628,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44741</v>
+        <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.9</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.3</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46176</v>
+        <v>46286</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45104</v>
+        <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.1</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45232</v>
+        <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45427</v>
+        <v>46176</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2482-2025</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45674</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,556 +1669,556 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 58350-2025</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>6.9</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="D15" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
       <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
         <v/>
@@ -2268,7 +2268,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,35 +2853,39 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -2905,7 +2909,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2997,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3010,7 +3014,7 @@
         <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3023,16 +3027,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3047,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3063,39 +3067,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
         <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45427</v>
+        <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45104</v>
+        <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45117</v>
+        <v>45427</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45240</v>
+        <v>46021</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44907</v>
+        <v>45005</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45463</v>
+        <v>44524</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46021</v>
+        <v>45030</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46021</v>
+        <v>44907</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>8.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44897</v>
+        <v>45401</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8.9</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45233</v>
+        <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45400</v>
+        <v>45048</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45950</v>
+        <v>45406</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>13.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46191</v>
+        <v>45233</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45117</v>
+        <v>45428</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45401</v>
+        <v>45232</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45428</v>
+        <v>45240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44741</v>
+        <v>45950</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45406</v>
+        <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>13.5</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45005</v>
+        <v>46191</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45048</v>
+        <v>45400</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45232</v>
+        <v>44741</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>8.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44524</v>
+        <v>45104</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45030</v>
+        <v>45232</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5774,7 +5774,7 @@
         <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5847,7 +5847,7 @@
         <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5920,7 +5920,7 @@
         <v>46286</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>46176</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2482-2025</t>
+          <t>A 38011-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45674</v>
+        <v>45160</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -1897,248 +1897,248 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 58350-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>6.9</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
         <v/>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         <v>46070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,46 +2853,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2906,10 +2902,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45030</v>
+        <v>45401</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,10 +2918,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2934,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2946,58 +2942,62 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>45030</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.1</v>
+        <v>6.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3054,48 +3054,48 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
         <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45463</v>
+        <v>44907</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45117</v>
+        <v>45400</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45427</v>
+        <v>45463</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3723,14 +3723,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46021</v>
+        <v>45005</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3796,14 +3796,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45117</v>
+        <v>45048</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45005</v>
+        <v>45232</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>44524</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45030</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44907</v>
+        <v>45427</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44897</v>
+        <v>45104</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4241,7 +4241,7 @@
         <v>44897</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45401</v>
+        <v>44897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46021</v>
+        <v>45232</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46021</v>
+        <v>45240</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45048</v>
+        <v>45401</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45406</v>
+        <v>45428</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>13.5</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45233</v>
+        <v>44741</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>8.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45428</v>
+        <v>45233</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45232</v>
+        <v>45406</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>13.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45240</v>
+        <v>45232</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45950</v>
+        <v>46021</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46191</v>
+        <v>46021</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45400</v>
+        <v>46021</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44741</v>
+        <v>46021</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.9</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45104</v>
+        <v>45950</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45232</v>
+        <v>46191</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5774,7 +5774,7 @@
         <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5847,7 +5847,7 @@
         <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5920,7 +5920,7 @@
         <v>46286</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>46176</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38011-2023</t>
+          <t>A 58350-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45160</v>
+        <v>45985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>6.9</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -1893,252 +1893,252 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lökgroda
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         <v>46070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,42 +2853,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2902,10 +2906,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45401</v>
+        <v>46286</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2918,7 +2922,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2930,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2942,10 +2946,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2958,39 +2962,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
         <v>45030</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46286</v>
+        <v>45401</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>11.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3159,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3172,35 +3172,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44907</v>
+        <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45400</v>
+        <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45463</v>
+        <v>45427</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3723,14 +3723,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45005</v>
+        <v>46021</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3796,14 +3796,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45048</v>
+        <v>45117</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45232</v>
+        <v>45005</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>44524</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45030</v>
+        <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45427</v>
+        <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45104</v>
+        <v>46021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.9</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44897</v>
+        <v>45030</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45117</v>
+        <v>44907</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45117</v>
+        <v>44897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>8.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45232</v>
+        <v>44897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45240</v>
+        <v>45401</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45401</v>
+        <v>45048</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45428</v>
+        <v>45406</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>13.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44741</v>
+        <v>45233</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.9</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45233</v>
+        <v>45950</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45406</v>
+        <v>45428</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>13.5</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45232</v>
+        <v>46191</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46021</v>
+        <v>45232</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46021</v>
+        <v>45240</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46021</v>
+        <v>45232</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46021</v>
+        <v>45400</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46021</v>
+        <v>44741</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>8.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45950</v>
+        <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46191</v>
+        <v>46286</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5628,7 +5628,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5701,7 +5701,7 @@
         <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5774,7 +5774,7 @@
         <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46286</v>
+        <v>45104</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>8.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5993,7 +5993,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46181</v>
+        <v>46176</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46176</v>
+        <v>45232</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 2482-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 15565-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,46 +2853,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2906,10 +2902,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46286</v>
+        <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,10 +2918,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2955,49 +2951,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3007,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45030</v>
+        <v>46286</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,10 +3023,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3060,49 +3056,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3112,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45401</v>
+        <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,16 +3128,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3156,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3172,42 +3168,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3221,10 +3217,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46174</v>
+        <v>45401</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,13 +3233,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3277,35 +3273,39 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45463</v>
+        <v>45427</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45117</v>
+        <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45427</v>
+        <v>46021</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45117</v>
+        <v>45240</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45005</v>
+        <v>46021</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44524</v>
+        <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4022,7 +4022,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4095,7 +4095,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46021</v>
+        <v>44907</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46021</v>
+        <v>45463</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45030</v>
+        <v>44897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44907</v>
+        <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44897</v>
+        <v>45232</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44897</v>
+        <v>45233</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45401</v>
+        <v>45232</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45048</v>
+        <v>45950</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45406</v>
+        <v>45400</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>13.5</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45233</v>
+        <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45950</v>
+        <v>46286</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45428</v>
+        <v>46286</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46191</v>
+        <v>45117</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45240</v>
+        <v>46286</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45400</v>
+        <v>46181</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44741</v>
+        <v>46176</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46286</v>
+        <v>45401</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46286</v>
+        <v>45428</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46286</v>
+        <v>44741</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>8.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46286</v>
+        <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>13.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5840,14 +5840,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46181</v>
+        <v>45005</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5913,14 +5913,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45104</v>
+        <v>45048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46181</v>
+        <v>45232</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46176</v>
+        <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45232</v>
+        <v>45030</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46070</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45160</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45985</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45401</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>46286</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45401</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45427</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>46021</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45240</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>46021</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44907</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45463</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45232</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45233</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45232</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45950</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>45400</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>46286</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>46286</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45117</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>46286</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>46286</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>46181</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>46176</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>45401</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45428</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44741</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>46181</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45005</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>45048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45232</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>45030</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46070</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45160</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45985</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45401</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>46286</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45401</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45427</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>46021</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45240</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>46021</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44907</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45463</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45232</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45233</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45232</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45950</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>45400</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>46286</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>46286</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45117</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>46286</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>46286</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>46181</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>46176</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>45401</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45428</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44741</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>46181</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45005</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>45048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45232</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>45030</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2482-2025</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45674</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D14" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="D16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,35 +2853,39 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -2905,7 +2909,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2997,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3007,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46286</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3023,19 +3027,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>11.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3050,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3063,42 +3067,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3112,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46174</v>
+        <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3128,19 +3132,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3152,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3168,42 +3172,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3217,10 +3221,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45401</v>
+        <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3233,13 +3237,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3273,39 +3277,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45427</v>
+        <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45104</v>
+        <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3723,14 +3723,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45117</v>
+        <v>45005</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45240</v>
+        <v>44524</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>8.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46021</v>
+        <v>45030</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46021</v>
+        <v>44907</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>8.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44907</v>
+        <v>45401</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45463</v>
+        <v>46021</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4526,14 +4526,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45233</v>
+        <v>45048</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45232</v>
+        <v>45406</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>13.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45950</v>
+        <v>45233</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45400</v>
+        <v>46021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46191</v>
+        <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46286</v>
+        <v>45232</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46286</v>
+        <v>45950</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45117</v>
+        <v>45240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46286</v>
+        <v>45232</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46286</v>
+        <v>46191</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46286</v>
+        <v>45400</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46181</v>
+        <v>44741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46176</v>
+        <v>45104</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45401</v>
+        <v>45232</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45428</v>
+        <v>46286</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44741</v>
+        <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45406</v>
+        <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13.5</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5840,14 +5840,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45005</v>
+        <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5913,14 +5913,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45048</v>
+        <v>46176</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45232</v>
+        <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44524</v>
+        <v>45427</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8.1</v>
+        <v>3.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45030</v>
+        <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 2482-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 15565-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,39 +2853,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -2909,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2993,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3007,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>46286</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,19 +3023,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.1</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3054,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3067,42 +3063,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3112,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,19 +3128,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3156,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3172,42 +3168,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3221,10 +3217,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46174</v>
+        <v>45401</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,13 +3233,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3277,35 +3273,39 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45463</v>
+        <v>45104</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45117</v>
+        <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3723,14 +3723,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45005</v>
+        <v>46021</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44524</v>
+        <v>46021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45030</v>
+        <v>46021</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44907</v>
+        <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44897</v>
+        <v>44907</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.9</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45401</v>
+        <v>46021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46021</v>
+        <v>45950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46021</v>
+        <v>46191</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4526,14 +4526,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45048</v>
+        <v>45232</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45406</v>
+        <v>45233</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>13.5</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45233</v>
+        <v>45232</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46021</v>
+        <v>45400</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45428</v>
+        <v>46286</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45950</v>
+        <v>46286</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45240</v>
+        <v>46286</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46191</v>
+        <v>46176</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45400</v>
+        <v>45117</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44741</v>
+        <v>45401</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.9</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45104</v>
+        <v>45428</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45232</v>
+        <v>46181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46286</v>
+        <v>44741</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>8.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46286</v>
+        <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>13.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5767,14 +5767,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46286</v>
+        <v>45005</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5840,14 +5840,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46286</v>
+        <v>45048</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46176</v>
+        <v>45232</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46181</v>
+        <v>44524</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45427</v>
+        <v>45030</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46181</v>
+        <v>45427</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2482-2025</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45674</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 9570-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>46070</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>6.6</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,35 +2853,39 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -2905,7 +2909,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2997,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3007,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46286</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3023,19 +3027,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>11.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3050,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3063,42 +3067,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3112,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46174</v>
+        <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3128,19 +3132,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3152,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3168,42 +3172,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3217,10 +3221,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45401</v>
+        <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3233,13 +3237,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3273,39 +3277,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3504,14 +3504,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45104</v>
+        <v>45048</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45117</v>
+        <v>45406</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>13.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45240</v>
+        <v>45427</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46021</v>
+        <v>45463</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46021</v>
+        <v>45233</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44907</v>
+        <v>45005</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45463</v>
+        <v>44524</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46021</v>
+        <v>45030</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45950</v>
+        <v>45428</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46191</v>
+        <v>44907</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44897</v>
+        <v>45232</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8.9</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4460,7 +4460,7 @@
         <v>44897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45232</v>
+        <v>44897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45233</v>
+        <v>45401</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45232</v>
+        <v>45240</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45400</v>
+        <v>45232</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46286</v>
+        <v>46021</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>6.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46286</v>
+        <v>45950</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46286</v>
+        <v>46021</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46286</v>
+        <v>46021</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46286</v>
+        <v>46021</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46176</v>
+        <v>46021</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45117</v>
+        <v>45400</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45401</v>
+        <v>46191</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45428</v>
+        <v>44741</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>8.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46181</v>
+        <v>45104</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44741</v>
+        <v>45232</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45406</v>
+        <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5767,14 +5767,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45005</v>
+        <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5840,14 +5840,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45048</v>
+        <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44524</v>
+        <v>46176</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.1</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45030</v>
+        <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45427</v>
+        <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 2482-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,662 +1669,662 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 15565-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U14" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D15" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
       <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
         <v/>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,39 +2853,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -2909,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2993,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3014,7 +3010,7 @@
         <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,16 +3023,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3051,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3067,35 +3063,39 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
         <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3504,14 +3504,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45048</v>
+        <v>45104</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>8.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45406</v>
+        <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>13.5</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45427</v>
+        <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45463</v>
+        <v>44907</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45233</v>
+        <v>45463</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45117</v>
+        <v>44897</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>8.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45117</v>
+        <v>44897</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45005</v>
+        <v>45232</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44524</v>
+        <v>45233</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45030</v>
+        <v>46021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45428</v>
+        <v>45232</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44907</v>
+        <v>46021</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4599,14 +4599,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45401</v>
+        <v>45400</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45240</v>
+        <v>45950</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45232</v>
+        <v>45117</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46021</v>
+        <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45950</v>
+        <v>45401</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46021</v>
+        <v>45428</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46021</v>
+        <v>44741</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>8.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46021</v>
+        <v>45406</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>13.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46021</v>
+        <v>45005</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45400</v>
+        <v>45048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46191</v>
+        <v>45232</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44741</v>
+        <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45104</v>
+        <v>45030</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5628,7 +5628,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5701,7 +5701,7 @@
         <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46286</v>
+        <v>45427</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5847,7 +5847,7 @@
         <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5920,7 +5920,7 @@
         <v>46286</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46181</v>
+        <v>46176</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2482-2025</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45674</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D15" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="D17" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Mindre tåtelsmygare
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45030</v>
+        <v>45401</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2942,58 +2942,62 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3007,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>45030</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3023,10 +3027,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3035,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3047,55 +3051,51 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
         <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45104</v>
+        <v>45406</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.1</v>
+        <v>13.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45117</v>
+        <v>45233</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45240</v>
+        <v>45463</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44907</v>
+        <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45463</v>
+        <v>45117</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44897</v>
+        <v>45005</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.9</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44897</v>
+        <v>44524</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45232</v>
+        <v>45030</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45233</v>
+        <v>45427</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46021</v>
+        <v>44907</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45232</v>
+        <v>44897</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>8.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46021</v>
+        <v>45428</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46021</v>
+        <v>45232</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46021</v>
+        <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4599,14 +4599,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45400</v>
+        <v>45240</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45950</v>
+        <v>45232</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45117</v>
+        <v>45048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4818,14 +4818,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46191</v>
+        <v>45400</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45401</v>
+        <v>44741</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>8.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45428</v>
+        <v>46021</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44741</v>
+        <v>45104</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45406</v>
+        <v>45232</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45005</v>
+        <v>46021</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45048</v>
+        <v>46021</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44524</v>
+        <v>46021</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45030</v>
+        <v>45950</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46286</v>
+        <v>46191</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5628,7 +5628,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5701,7 +5701,7 @@
         <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45427</v>
+        <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5847,7 +5847,7 @@
         <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5920,7 +5920,7 @@
         <v>46286</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5993,7 +5993,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.3</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
         <v>46176</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6139,7 +6139,7 @@
         <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45401</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45985</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>46070</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45674</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>46286</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45401</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46306</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45240</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>44907</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45463</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>44897</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44897</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>45232</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45233</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45232</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45950</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45400</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>46021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>46021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45117</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>45401</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45428</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44741</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>45406</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>46286</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>46286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>46286</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45005</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45048</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>45232</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>45427</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>46176</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>46181</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45401</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45985</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>46070</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45674</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>46286</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45401</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46306</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45240</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>44907</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45463</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>44897</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44897</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>45232</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45233</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45232</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45950</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45400</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>46021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>46021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45117</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>45401</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45428</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44741</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>45406</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>46286</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>46286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>46286</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45005</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45048</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>45232</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>45427</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>46176</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>46181</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 31697-2023</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45117</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,288 +1645,288 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 38011-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>45160</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>2.8</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Lökgroda
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
         <v>45985</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>46070</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45674</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,35 +2853,39 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -2905,7 +2909,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2997,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3007,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46286</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3023,19 +3027,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>11.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3050,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3063,42 +3067,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3112,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45401</v>
+        <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3128,7 +3132,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3140,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3152,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3168,39 +3172,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46306</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45104</v>
+        <v>45463</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
         <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45240</v>
+        <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3828,14 +3828,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44907</v>
+        <v>45005</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45463</v>
+        <v>44524</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3964,7 +3964,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44897</v>
+        <v>45030</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44897</v>
+        <v>44907</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45232</v>
+        <v>44897</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45233</v>
+        <v>44897</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4256,7 +4256,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45232</v>
+        <v>45401</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4329,7 +4329,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4339,14 +4339,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45950</v>
+        <v>45048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46021</v>
+        <v>45406</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4475,7 +4475,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4485,14 +4485,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45400</v>
+        <v>45233</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46021</v>
+        <v>45950</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4638,7 +4638,7 @@
         <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46021</v>
+        <v>45428</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4767,7 +4767,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46021</v>
+        <v>45232</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46191</v>
+        <v>46021</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45117</v>
+        <v>46021</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4986,7 +4986,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45401</v>
+        <v>46021</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45428</v>
+        <v>46021</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5132,7 +5132,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44741</v>
+        <v>45240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45406</v>
+        <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>13.5</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46286</v>
+        <v>46191</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46286</v>
+        <v>45400</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5424,7 +5424,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46286</v>
+        <v>44741</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>8.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5497,7 +5497,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46286</v>
+        <v>45104</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>8.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5570,7 +5570,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46286</v>
+        <v>45232</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5653,14 +5653,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45005</v>
+        <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5726,14 +5726,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45048</v>
+        <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5789,7 +5789,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44524</v>
+        <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.1</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45030</v>
+        <v>46286</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
         <v>45427</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6098,7 +6098,7 @@
         <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.3</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6154,7 +6154,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46181</v>
+        <v>46176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 2482-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 15565-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,39 +2853,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -2909,7 +2905,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2993,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3007,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>46286</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,19 +3023,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.1</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3054,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3067,42 +3063,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3112,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,19 +3128,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3156,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3172,42 +3168,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 42218-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3221,10 +3217,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46174</v>
+        <v>46306</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,19 +3233,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3261,10 +3257,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3277,42 +3273,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 42218-2026 artfynd.xlsx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 42218-2026 karta.png", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 42218-2026 georefererad karta.tif", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 42218-2026 FSC-klagomål.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 42218-2026 FSC-klagomål mail.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 42218-2026 tillsynsbegäran.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 42218-2026 tillsynsbegäran mail.docx", "A 42218-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42218-2026</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3326,10 +3322,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46306</v>
+        <v>45401</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3338,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3354,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3366,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3382,35 +3378,39 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 42218-2026 artfynd.xlsx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 42218-2026 karta.png", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 42218-2026 georefererad karta.tif", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 42218-2026 FSC-klagomål.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 42218-2026 FSC-klagomål mail.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 42218-2026 tillsynsbegäran.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 42218-2026 tillsynsbegäran mail.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45463</v>
+        <v>45427</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45117</v>
+        <v>45104</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45117</v>
+        <v>46021</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3828,14 +3828,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45005</v>
+        <v>45117</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44524</v>
+        <v>45240</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3964,7 +3964,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45030</v>
+        <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44907</v>
+        <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4256,7 +4256,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45401</v>
+        <v>44907</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4329,7 +4329,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4339,14 +4339,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45048</v>
+        <v>45463</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45406</v>
+        <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>13.5</v>
+        <v>8.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4475,7 +4475,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45233</v>
+        <v>44897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45950</v>
+        <v>45232</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46021</v>
+        <v>45950</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45428</v>
+        <v>45233</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4784,7 +4784,7 @@
         <v>45232</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46021</v>
+        <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4923,14 +4923,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46021</v>
+        <v>45400</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4986,7 +4986,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46021</v>
+        <v>46286</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46021</v>
+        <v>46286</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5132,7 +5132,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45240</v>
+        <v>46286</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46191</v>
+        <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45400</v>
+        <v>45117</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5424,7 +5424,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44741</v>
+        <v>45401</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.9</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5497,7 +5497,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45104</v>
+        <v>45428</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5570,7 +5570,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45232</v>
+        <v>44741</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46286</v>
+        <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>13.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5789,7 +5789,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5872,14 +5872,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46286</v>
+        <v>45005</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46286</v>
+        <v>46176</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6008,7 +6008,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6018,14 +6018,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45427</v>
+        <v>45048</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6081,7 +6081,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46181</v>
+        <v>45232</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6154,7 +6154,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46181</v>
+        <v>44524</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46176</v>
+        <v>45030</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2482-2025</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45674</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D14" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="D17" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Mindre tåtelsmygare
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,35 +2853,39 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
@@ -2905,7 +2909,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2997,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3007,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46286</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3023,19 +3027,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>11.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3050,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3063,42 +3067,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3112,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46174</v>
+        <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3128,19 +3132,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3152,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3168,42 +3172,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42218-2026</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3217,10 +3221,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46306</v>
+        <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3233,19 +3237,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3257,10 +3261,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3273,42 +3277,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 42218-2026 artfynd.xlsx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 42218-2026 karta.png", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 42218-2026 georefererad karta.tif", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 42218-2026 FSC-klagomål.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 42218-2026 FSC-klagomål mail.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 42218-2026 tillsynsbegäran.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 42218-2026 tillsynsbegäran mail.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 42218-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3322,10 +3326,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45401</v>
+        <v>46306</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3338,7 +3342,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3350,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3362,10 +3366,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3378,39 +3382,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 42218-2026 artfynd.xlsx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 42218-2026 karta.png", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 42218-2026 georefererad karta.tif", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 42218-2026 FSC-klagomål.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 42218-2026 FSC-klagomål mail.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 42218-2026 tillsynsbegäran.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 42218-2026 tillsynsbegäran mail.docx", "A 42218-2026")</f>
         <v/>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45427</v>
+        <v>45463</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45104</v>
+        <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46021</v>
+        <v>45427</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3835,7 +3835,7 @@
         <v>45117</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45240</v>
+        <v>46021</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3964,7 +3964,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3974,14 +3974,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46021</v>
+        <v>45005</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46021</v>
+        <v>44524</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46021</v>
+        <v>45030</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46021</v>
+        <v>44907</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4256,7 +4256,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44907</v>
+        <v>44897</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>8.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4329,7 +4329,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44897</v>
+        <v>45401</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8.9</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4475,7 +4475,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45950</v>
+        <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45233</v>
+        <v>46021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4767,7 +4767,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4777,14 +4777,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45232</v>
+        <v>45048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46191</v>
+        <v>45406</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>13.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4923,14 +4923,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45400</v>
+        <v>45233</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4986,7 +4986,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46286</v>
+        <v>45428</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46286</v>
+        <v>45232</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5132,7 +5132,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46286</v>
+        <v>45240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46286</v>
+        <v>45950</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46286</v>
+        <v>45232</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45117</v>
+        <v>46191</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5424,7 +5424,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5434,14 +5434,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45401</v>
+        <v>45400</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5497,7 +5497,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45428</v>
+        <v>44741</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>8.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5570,7 +5570,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44741</v>
+        <v>45104</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46181</v>
+        <v>45232</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45406</v>
+        <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13.5</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5789,7 +5789,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5872,14 +5872,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45005</v>
+        <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46176</v>
+        <v>46286</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6008,7 +6008,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6018,14 +6018,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45048</v>
+        <v>46286</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6081,7 +6081,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45232</v>
+        <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6154,7 +6154,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44524</v>
+        <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45030</v>
+        <v>46176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 27244-2024</t>
+          <t>A 25049-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45471</v>
+        <v>46174</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1120,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1132,9 +1132,122 @@
         <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Vit stork
+Bivråk
+Fiskgjuse
+Havsörn
+Trana</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25049-2026 artfynd.xlsx", "A 25049-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25049-2026 karta.png", "A 25049-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25049-2026 georefererad karta.tif", "A 25049-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25049-2026 FSC-klagomål.docx", "A 25049-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25049-2026 FSC-klagomål mail.docx", "A 25049-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25049-2026 tillsynsbegäran.docx", "A 25049-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25049-2026 tillsynsbegäran mail.docx", "A 25049-2026")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 25049-2026 prioriterade fågelarter.docx", "A 25049-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 27244-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45471</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Desmeknopp
 Kragjordstjärna
@@ -1143,152 +1256,39 @@
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 27244-2024 artfynd.xlsx", "A 27244-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 27244-2024 karta.png", "A 27244-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 27244-2024 georefererad karta.tif", "A 27244-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 27244-2024 FSC-klagomål.docx", "A 27244-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 27244-2024 FSC-klagomål mail.docx", "A 27244-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 27244-2024 tillsynsbegäran.docx", "A 27244-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 27244-2024 tillsynsbegäran mail.docx", "A 27244-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 25049-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Vit stork
-Bivråk
-Fiskgjuse
-Havsörn
-Trana</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25049-2026 artfynd.xlsx", "A 25049-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25049-2026 karta.png", "A 25049-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25049-2026 georefererad karta.tif", "A 25049-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25049-2026 FSC-klagomål.docx", "A 25049-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25049-2026 FSC-klagomål mail.docx", "A 25049-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25049-2026 tillsynsbegäran.docx", "A 25049-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25049-2026 tillsynsbegäran mail.docx", "A 25049-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 25049-2026 prioriterade fågelarter.docx", "A 25049-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14150-2023</t>
+          <t>A 31700-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45009</v>
+        <v>45117</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1318,22 +1318,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1342,10 +1342,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1354,9 +1354,121 @@
         <v>7</v>
       </c>
       <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Brun glada
+Revig blodrot
+Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31700-2023 artfynd.xlsx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31700-2023 karta.png", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31700-2023 georefererad karta.tif", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31700-2023 FSC-klagomål.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31700-2023 FSC-klagomål mail.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31700-2023 tillsynsbegäran.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31700-2023 tillsynsbegäran mail.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 31700-2023 prioriterade fågelarter.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 14150-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45009</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Guldlockmossa
 Lönnlav
@@ -1364,144 +1476,32 @@
 Tibast</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 14150-2023 artfynd.xlsx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 14150-2023 karta.png", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 14150-2023 georefererad karta.tif", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 14150-2023 FSC-klagomål.docx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 14150-2023 FSC-klagomål mail.docx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 14150-2023 tillsynsbegäran.docx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 14150-2023 tillsynsbegäran mail.docx", "A 14150-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 31700-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Brun glada
-Revig blodrot
-Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31700-2023 artfynd.xlsx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31700-2023 karta.png", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31700-2023 georefererad karta.tif", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31700-2023 FSC-klagomål.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31700-2023 FSC-klagomål mail.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31700-2023 tillsynsbegäran.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31700-2023 tillsynsbegäran mail.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 31700-2023 prioriterade fågelarter.docx", "A 31700-2023")</f>
         <v/>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 2482-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,556 +1669,556 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 15565-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U14" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D15" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
       <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
         <v/>
@@ -2268,7 +2268,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,46 +2853,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2906,10 +2902,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45030</v>
+        <v>45401</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,10 +2918,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2934,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2946,58 +2942,62 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>46286</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,19 +3027,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.1</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3067,42 +3067,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46286</v>
+        <v>45030</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3165,42 +3165,42 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46306</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45463</v>
+        <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3689,7 +3689,7 @@
         <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45427</v>
+        <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45117</v>
+        <v>45428</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3964,7 +3964,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3974,14 +3974,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45005</v>
+        <v>44741</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>8.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44524</v>
+        <v>45406</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.1</v>
+        <v>13.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45030</v>
+        <v>45005</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4193,14 +4193,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44907</v>
+        <v>45048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4256,7 +4256,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.9</v>
+        <v>6.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4329,7 +4329,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44897</v>
+        <v>45232</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45401</v>
+        <v>44524</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4475,7 +4475,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46021</v>
+        <v>45950</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46021</v>
+        <v>45240</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46021</v>
+        <v>45030</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4711,7 +4711,7 @@
         <v>46021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4767,7 +4767,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4777,14 +4777,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45048</v>
+        <v>46021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45406</v>
+        <v>46021</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>13.5</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45233</v>
+        <v>46021</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4986,7 +4986,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45428</v>
+        <v>45427</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45232</v>
+        <v>46191</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5132,7 +5132,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45240</v>
+        <v>46176</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45950</v>
+        <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45232</v>
+        <v>45463</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46191</v>
+        <v>46286</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5424,7 +5424,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5434,14 +5434,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45400</v>
+        <v>46286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5497,7 +5497,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44741</v>
+        <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.9</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5570,7 +5570,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45104</v>
+        <v>46286</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.1</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46286</v>
+        <v>44897</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>8.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5789,7 +5789,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46286</v>
+        <v>44897</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46286</v>
+        <v>45232</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>7.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6008,7 +6008,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6081,7 +6081,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46181</v>
+        <v>45233</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6154,7 +6154,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46181</v>
+        <v>45232</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6237,14 +6237,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46176</v>
+        <v>45400</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25049-2026</t>
+          <t>A 27244-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46174</v>
+        <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1120,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1132,9 +1132,118 @@
         <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Desmeknopp
+Kragjordstjärna
+Scharlakansskål
+Stor häxört
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 27244-2024 artfynd.xlsx", "A 27244-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 27244-2024 karta.png", "A 27244-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 27244-2024 georefererad karta.tif", "A 27244-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 27244-2024 FSC-klagomål.docx", "A 27244-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 27244-2024 FSC-klagomål mail.docx", "A 27244-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 27244-2024 tillsynsbegäran.docx", "A 27244-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 27244-2024 tillsynsbegäran mail.docx", "A 27244-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 25049-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Vit stork
 Bivråk
@@ -1143,145 +1252,36 @@
 Trana</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25049-2026 artfynd.xlsx", "A 25049-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25049-2026 karta.png", "A 25049-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25049-2026 georefererad karta.tif", "A 25049-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25049-2026 FSC-klagomål.docx", "A 25049-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25049-2026 FSC-klagomål mail.docx", "A 25049-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25049-2026 tillsynsbegäran.docx", "A 25049-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25049-2026 tillsynsbegäran mail.docx", "A 25049-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 25049-2026 prioriterade fågelarter.docx", "A 25049-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 27244-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45471</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Desmeknopp
-Kragjordstjärna
-Scharlakansskål
-Stor häxört
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 27244-2024 artfynd.xlsx", "A 27244-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 27244-2024 karta.png", "A 27244-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 27244-2024 georefererad karta.tif", "A 27244-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 27244-2024 FSC-klagomål.docx", "A 27244-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 27244-2024 FSC-klagomål mail.docx", "A 27244-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 27244-2024 tillsynsbegäran.docx", "A 27244-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 27244-2024 tillsynsbegäran mail.docx", "A 27244-2024")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>45117</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45009</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2482-2025</t>
+          <t>A 15565-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45674</v>
+        <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="D16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Lökgroda
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 15565-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45401</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Igelkott</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15565-2024 artfynd.xlsx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15565-2024 karta.png", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15565-2024 georefererad karta.tif", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15565-2024 FSC-klagomål.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15565-2024 FSC-klagomål mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15565-2024 tillsynsbegäran.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15565-2024 tillsynsbegäran mail.docx", "A 15565-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,42 +2853,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2902,10 +2906,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45401</v>
+        <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2918,10 +2922,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2930,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2942,62 +2946,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46286</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,19 +3027,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>11.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3067,42 +3067,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45030</v>
+        <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3165,49 +3165,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25054-2026</t>
+          <t>A 42218-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46174</v>
+        <v>46306</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,19 +3237,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3261,10 +3261,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3277,42 +3277,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 42218-2026 artfynd.xlsx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 42218-2026 karta.png", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 42218-2026 georefererad karta.tif", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 42218-2026 FSC-klagomål.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 42218-2026 FSC-klagomål mail.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 42218-2026 tillsynsbegäran.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 42218-2026 tillsynsbegäran mail.docx", "A 42218-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42218-2026</t>
+          <t>A 25054-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46306</v>
+        <v>46174</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,19 +3342,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3366,10 +3366,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3382,35 +3382,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 42218-2026 artfynd.xlsx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25054-2026 artfynd.xlsx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 42218-2026 karta.png", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25054-2026 karta.png", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 42218-2026 georefererad karta.tif", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25054-2026 georefererad karta.tif", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 42218-2026 FSC-klagomål.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25054-2026 FSC-klagomål.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 42218-2026 FSC-klagomål mail.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25054-2026 FSC-klagomål mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 42218-2026 tillsynsbegäran.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25054-2026 tillsynsbegäran.docx", "A 25054-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 42218-2026 tillsynsbegäran mail.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25054-2026 tillsynsbegäran mail.docx", "A 25054-2026")</f>
         <v/>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45117</v>
+        <v>45950</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45401</v>
+        <v>45232</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45428</v>
+        <v>45463</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
         <v>45117</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44741</v>
+        <v>46191</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.9</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45406</v>
+        <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45005</v>
+        <v>45427</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4193,14 +4193,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45048</v>
+        <v>46286</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4256,7 +4256,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46021</v>
+        <v>46286</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4329,7 +4329,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45232</v>
+        <v>45117</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44524</v>
+        <v>46286</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8.1</v>
+        <v>0.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4475,7 +4475,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45950</v>
+        <v>46286</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45240</v>
+        <v>46286</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45030</v>
+        <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4711,7 +4711,7 @@
         <v>46021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4767,7 +4767,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4784,7 +4784,7 @@
         <v>46021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4857,7 +4857,7 @@
         <v>46021</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4923,14 +4923,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46021</v>
+        <v>45005</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4986,7 +4986,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45427</v>
+        <v>44524</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>8.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46191</v>
+        <v>45030</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
         <v>46176</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44907</v>
+        <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45463</v>
+        <v>44907</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46286</v>
+        <v>44897</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>8.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5424,7 +5424,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46286</v>
+        <v>44897</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46286</v>
+        <v>46181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5570,7 +5570,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46286</v>
+        <v>45401</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5653,14 +5653,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46286</v>
+        <v>45048</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44897</v>
+        <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.9</v>
+        <v>13.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5789,7 +5789,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44897</v>
+        <v>45233</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45232</v>
+        <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46181</v>
+        <v>45232</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6008,7 +6008,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46181</v>
+        <v>45240</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6081,7 +6081,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45233</v>
+        <v>45232</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6154,7 +6154,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6164,14 +6164,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45232</v>
+        <v>45400</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6237,14 +6237,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45400</v>
+        <v>44741</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>8.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45117</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45009</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>46070</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45674</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45160</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46306</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46174</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45950</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45232</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>45463</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45117</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>46191</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>45427</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>46286</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46286</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45117</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>46286</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>46286</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>46286</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>46021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>46021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46021</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45005</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44524</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45030</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>46176</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44907</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44897</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44897</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>46181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>45401</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45048</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>45233</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>45232</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>45240</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45232</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>45400</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>44741</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>9</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45117</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45009</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>46070</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45674</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45160</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46306</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46174</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45950</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45232</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>45463</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45117</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>46191</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>45427</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>46286</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46286</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45117</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>46286</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>46286</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>46286</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>46021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>46021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46021</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45005</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44524</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45030</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>46176</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44907</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44897</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44897</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>46181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>45401</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45048</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>45233</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>45232</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>45240</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45232</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>45400</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>44741</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31700-2023</t>
+          <t>A 14150-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45117</v>
+        <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1318,22 +1318,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1342,10 +1342,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1354,9 +1354,117 @@
         <v>7</v>
       </c>
       <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Guldlockmossa
+Lönnlav
+Platt fjädermossa
+Tibast</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 14150-2023 artfynd.xlsx", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 14150-2023 karta.png", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 14150-2023 georefererad karta.tif", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 14150-2023 FSC-klagomål.docx", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 14150-2023 FSC-klagomål mail.docx", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 14150-2023 tillsynsbegäran.docx", "A 14150-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 14150-2023 tillsynsbegäran mail.docx", "A 14150-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 31700-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Brun glada
 Revig blodrot
@@ -1364,144 +1472,36 @@
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31700-2023 artfynd.xlsx", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31700-2023 karta.png", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31700-2023 georefererad karta.tif", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31700-2023 FSC-klagomål.docx", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31700-2023 FSC-klagomål mail.docx", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31700-2023 tillsynsbegäran.docx", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31700-2023 tillsynsbegäran mail.docx", "A 31700-2023")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 31700-2023 prioriterade fågelarter.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 14150-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45009</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Guldlockmossa
-Lönnlav
-Platt fjädermossa
-Tibast</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 14150-2023 artfynd.xlsx", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 14150-2023 karta.png", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 14150-2023 georefererad karta.tif", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 14150-2023 FSC-klagomål.docx", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 14150-2023 FSC-klagomål mail.docx", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 14150-2023 tillsynsbegäran.docx", "A 14150-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 14150-2023 tillsynsbegäran mail.docx", "A 14150-2023")</f>
         <v/>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 31697-2023</t>
+          <t>A 2482-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45117</v>
+        <v>45674</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1751,16 +1751,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1791,361 +1791,361 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="D15" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 2482-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45674</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Korallticka
-Ekoxe</t>
-        </is>
-      </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25022-2026</t>
+          <t>A 38011-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46174</v>
+        <v>45160</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -2208,149 +2208,149 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Mindre tåtelsmygare
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,46 +2853,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2906,10 +2902,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45030</v>
+        <v>45401</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,10 +2918,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2934,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2946,58 +2942,62 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>45030</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.1</v>
+        <v>6.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3054,48 +3054,48 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
         <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46306</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46174</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3609,14 +3609,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45104</v>
+        <v>45005</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.1</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3682,14 +3682,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45950</v>
+        <v>45048</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45232</v>
+        <v>45104</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45463</v>
+        <v>46191</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45117</v>
+        <v>45232</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3964,7 +3964,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46191</v>
+        <v>44524</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>8.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46021</v>
+        <v>45030</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45427</v>
+        <v>45117</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46286</v>
+        <v>45240</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4256,7 +4256,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46286</v>
+        <v>45427</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4329,7 +4329,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 59432-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45117</v>
+        <v>44907</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46286</v>
+        <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4475,7 +4475,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46286</v>
+        <v>46021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46286</v>
+        <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4638,7 +4638,7 @@
         <v>46021</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
         <v>46021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4784,7 +4784,7 @@
         <v>46021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>8.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4923,14 +4923,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45005</v>
+        <v>44897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4986,7 +4986,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44524</v>
+        <v>45232</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45030</v>
+        <v>46286</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5132,7 +5132,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46176</v>
+        <v>46286</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46181</v>
+        <v>46286</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59432-2022</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44907</v>
+        <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44897</v>
+        <v>46286</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.9</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5424,7 +5424,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44897</v>
+        <v>45233</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5497,7 +5497,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46181</v>
+        <v>45232</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5570,7 +5570,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5580,14 +5580,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45401</v>
+        <v>45400</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5653,14 +5653,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45048</v>
+        <v>45950</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45406</v>
+        <v>45117</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5789,7 +5789,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45233</v>
+        <v>45401</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45232</v>
+        <v>44741</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>8.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6008,7 +6008,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45240</v>
+        <v>46176</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6081,7 +6081,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45232</v>
+        <v>45406</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>13.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6154,7 +6154,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6164,14 +6164,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45400</v>
+        <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44741</v>
+        <v>46181</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>8.9</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45117</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45401</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2482-2025</t>
+          <t>A 31697-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45674</v>
+        <v>45117</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1751,16 +1751,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1791,566 +1791,566 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lökgroda
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 58350-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9570-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25022-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 2482-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>Korallticka
 Ekoxe</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58350-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 58350-2025 artfynd.xlsx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 58350-2025 karta.png", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 58350-2025 georefererad karta.tif", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 58350-2025 FSC-klagomål.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 58350-2025 FSC-klagomål mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 58350-2025 tillsynsbegäran.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 58350-2025 tillsynsbegäran mail.docx", "A 58350-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9570-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 9570-2026 artfynd.xlsx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 9570-2026 karta.png", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 9570-2026 georefererad karta.tif", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 9570-2026 FSC-klagomål.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 9570-2026 FSC-klagomål mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 9570-2026 tillsynsbegäran.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 9570-2026 tillsynsbegäran mail.docx", "A 9570-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 31697-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 38011-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45160</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lökgroda
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38011-2023 artfynd.xlsx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38011-2023 karta.png", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38011-2023 georefererad karta.tif", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38011-2023 FSC-klagomål.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38011-2023 FSC-klagomål mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38011-2023 tillsynsbegäran.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38011-2023 tillsynsbegäran mail.docx", "A 38011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 25022-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 25022-2026 artfynd.xlsx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 25022-2026 karta.png", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 25022-2026 georefererad karta.tif", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 25022-2026 FSC-klagomål.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 25022-2026 FSC-klagomål mail.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 25022-2026 tillsynsbegäran.docx", "A 25022-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 25022-2026 tillsynsbegäran mail.docx", "A 25022-2026")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>46213</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46213</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15571-2024</t>
+          <t>A 15582-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>45401</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,16 +2813,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2853,42 +2853,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15582-2024</t>
+          <t>A 38846-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2902,10 +2906,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45401</v>
+        <v>46286</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2918,7 +2922,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2930,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2942,10 +2946,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2958,46 +2962,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15582-2024 artfynd.xlsx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15582-2024 karta.png", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15582-2024 georefererad karta.tif", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15582-2024 FSC-klagomål.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15582-2024 FSC-klagomål mail.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15582-2024 tillsynsbegäran.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15582-2024 tillsynsbegäran mail.docx", "A 15582-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 15582-2024 prioriterade fågelarter.docx", "A 15582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16684-2023</t>
+          <t>A 42218-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45030</v>
+        <v>46306</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3060,49 +3060,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Större grynsnäcka</t>
+          <t>Buskvicker</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 42218-2026 artfynd.xlsx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 42218-2026 karta.png", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 42218-2026 georefererad karta.tif", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 42218-2026 FSC-klagomål.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 42218-2026 FSC-klagomål mail.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 42218-2026 tillsynsbegäran.docx", "A 42218-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 42218-2026 tillsynsbegäran mail.docx", "A 42218-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38846-2026</t>
+          <t>A 16684-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46286</v>
+        <v>45030</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3165,49 +3165,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Större grynsnäcka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 38846-2026 artfynd.xlsx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 16684-2023 artfynd.xlsx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 38846-2026 karta.png", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 16684-2023 karta.png", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 38846-2026 georefererad karta.tif", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 16684-2023 georefererad karta.tif", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 38846-2026 FSC-klagomål.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 16684-2023 FSC-klagomål.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 38846-2026 FSC-klagomål mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 16684-2023 FSC-klagomål mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 38846-2026 tillsynsbegäran.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 16684-2023 tillsynsbegäran.docx", "A 16684-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 38846-2026 tillsynsbegäran mail.docx", "A 38846-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 16684-2023 tillsynsbegäran mail.docx", "A 16684-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42218-2026</t>
+          <t>A 15571-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46306</v>
+        <v>45401</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,19 +3237,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>11.1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3277,35 +3277,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Buskvicker</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 42218-2026 artfynd.xlsx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 15571-2024 artfynd.xlsx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 42218-2026 karta.png", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 15571-2024 karta.png", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 42218-2026 georefererad karta.tif", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 15571-2024 georefererad karta.tif", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 42218-2026 FSC-klagomål.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 15571-2024 FSC-klagomål.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 42218-2026 FSC-klagomål mail.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 15571-2024 FSC-klagomål mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 42218-2026 tillsynsbegäran.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 15571-2024 tillsynsbegäran.docx", "A 15571-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 42218-2026 tillsynsbegäran mail.docx", "A 42218-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 15571-2024 tillsynsbegäran mail.docx", "A 15571-2024")</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>46174</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21072-2022</t>
+          <t>A 15577-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3536,14 +3536,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44704</v>
+        <v>45401</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3599,7 +3599,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13344-2023</t>
+          <t>A 21072-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45005</v>
+        <v>44704</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19190-2023</t>
+          <t>A 25603-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3682,14 +3682,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45048</v>
+        <v>45463</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 29030-2023</t>
+          <t>A 31701-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45104</v>
+        <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 27844-2026</t>
+          <t>A 31693-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46191</v>
+        <v>45117</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54284-2023</t>
+          <t>A 19190-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3901,14 +3901,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45232</v>
+        <v>45048</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3964,7 +3964,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 67456-2021</t>
+          <t>A 16199-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44524</v>
+        <v>45406</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.1</v>
+        <v>13.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16690-2023</t>
+          <t>A 13344-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45030</v>
+        <v>45005</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 31701-2023</t>
+          <t>A 54580-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45117</v>
+        <v>45233</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56202-2023</t>
+          <t>A 67456-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45240</v>
+        <v>44524</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>8.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4256,7 +4256,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18888-2024</t>
+          <t>A 16690-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45427</v>
+        <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
         <v>44907</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 25603-2024</t>
+          <t>A 57798-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4475,7 +4475,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64060-2025</t>
+          <t>A 57803-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46021</v>
+        <v>44897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64055-2025</t>
+          <t>A 64060-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4565,7 +4565,7 @@
         <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64058-2025</t>
+          <t>A 19268-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46021</v>
+        <v>45428</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64051-2025</t>
+          <t>A 18888-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46021</v>
+        <v>45427</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4767,7 +4767,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64049-2025</t>
+          <t>A 54284-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46021</v>
+        <v>45232</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57798-2022</t>
+          <t>A 56202-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44897</v>
+        <v>45240</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57803-2022</t>
+          <t>A 64049-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44897</v>
+        <v>46021</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4986,7 +4986,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54282-2023</t>
+          <t>A 64051-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45232</v>
+        <v>46021</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38844-2026</t>
+          <t>A 64055-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46286</v>
+        <v>46021</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5132,7 +5132,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38845-2026</t>
+          <t>A 64058-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46286</v>
+        <v>46021</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38842-2026</t>
+          <t>A 54280-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46286</v>
+        <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38841-2026</t>
+          <t>A 38844-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5295,7 +5295,7 @@
         <v>46286</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38847-2026</t>
+          <t>A 38845-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5368,7 +5368,7 @@
         <v>46286</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5424,7 +5424,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54580-2023</t>
+          <t>A 38841-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45233</v>
+        <v>46286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5497,7 +5497,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54280-2023</t>
+          <t>A 38847-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45232</v>
+        <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5570,7 +5570,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15277-2024</t>
+          <t>A 38842-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5580,14 +5580,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45400</v>
+        <v>46286</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 51318-2025</t>
+          <t>A 15277-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5653,14 +5653,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45950</v>
+        <v>45400</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31693-2023</t>
+          <t>A 27113-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45117</v>
+        <v>44741</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.1</v>
+        <v>8.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5789,7 +5789,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15577-2024</t>
+          <t>A 29030-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45401</v>
+        <v>45104</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19268-2024</t>
+          <t>A 54282-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45428</v>
+        <v>45232</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27113-2022</t>
+          <t>A 25275-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44741</v>
+        <v>46176</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6008,7 +6008,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25275-2026</t>
+          <t>A 26080-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6081,7 +6081,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16199-2024</t>
+          <t>A 26073-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45406</v>
+        <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>13.5</v>
+        <v>7.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6154,7 +6154,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26073-2026</t>
+          <t>A 51318-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46181</v>
+        <v>45950</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26080-2026</t>
+          <t>A 27844-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46181</v>
+        <v>46191</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt SVEDALA.xlsx
+++ b/Översikt SVEDALA.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45104</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>46174</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45471</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14150-2023</t>
+          <t>A 31700-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45009</v>
+        <v>45117</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1318,22 +1318,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1342,10 +1342,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1354,9 +1354,121 @@
         <v>7</v>
       </c>
       <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Brun glada
+Revig blodrot
+Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31700-2023 artfynd.xlsx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31700-2023 karta.png", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31700-2023 georefererad karta.tif", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31700-2023 FSC-klagomål.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31700-2023 FSC-klagomål mail.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31700-2023 tillsynsbegäran.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31700-2023 tillsynsbegäran mail.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 31700-2023 prioriterade fågelarter.docx", "A 31700-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 14150-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45009</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Guldlockmossa
 Lönnlav
@@ -1364,144 +1476,32 @@
 Tibast</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 14150-2023 artfynd.xlsx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 14150-2023 karta.png", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 14150-2023 georefererad karta.tif", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 14150-2023 FSC-klagomål.docx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 14150-2023 FSC-klagomål mail.docx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 14150-2023 tillsynsbegäran.docx", "A 14150-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 14150-2023 tillsynsbegäran mail.docx", "A 14150-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 31700-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SVEDALA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Brun glada
-Revig blodrot
-Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31700-2023 artfynd.xlsx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31700-2023 karta.png", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31700-2023 georefererad karta.tif", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31700-2023 FSC-klagomål.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31700-2023 FSC-klagomål mail.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31700-2023 tillsynsbegäran.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31700-2023 tillsynsbegäran mail.docx", "A 31700-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1263/fåglar/A 31700-2023 prioriterade fågelarter.docx", "A 31700-2023")</f>
         <v/>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>45406</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 15565-2024</t>
+          <t>A 2482-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45401</v>
+        <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1669,688 +1669,688 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Korallticka
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 2482-2025 artfynd.xlsx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 2482-2025 karta.png", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 2482-2025 georefererad karta.tif", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 2482-2025 FSC-klagomål.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 2482-2025 FSC-klagomål mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 2482-2025 tillsynsbegäran.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 2482-2025 tillsynsbegäran mail.docx", "A 2482-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31697-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/artfynd/A 31697-2023 artfynd.xlsx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor/A 31697-2023 karta.png", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/kartor_geotiff/A 31697-2023 georefererad karta.tif", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomål/A 31697-2023 FSC-klagomål.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/klagomålsmail/A 31697-2023 FSC-klagomål mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsyn/A 31697-2023 tillsynsbegäran.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1263/tillsynsmail/A 31697-2023 tillsynsbegäran mail.docx", "A 31697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38011-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45160</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SVEDALA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.8</v>
+      